--- a/isms-core-framework/A.5-organizational-controls/isms-a.5.12-13-classification-and-labelling/WKBK/90_workbooks/ISMS-IMP-A.5.12-13.S1_Classification_Scheme_Definition_20260208.xlsx
+++ b/isms-core-framework/A.5-organizational-controls/isms-a.5.12-13-classification-and-labelling/WKBK/90_workbooks/ISMS-IMP-A.5.12-13.S1_Classification_Scheme_Definition_20260208.xlsx
@@ -2361,7 +2361,7 @@
     <row r="8">
       <c r="A8" s="16" t="inlineStr">
         <is>
-          <t>PCI DSS</t>
+          <t>PCI DSS v4.0.1</t>
         </is>
       </c>
       <c r="B8" s="16" t="inlineStr">
